--- a/analyses/molecular-subtyping-methylation/input/mnp_v12.5_v12.8_NIHv2_v3.1_annotation_with_OPC_subtypes.xlsx
+++ b/analyses/molecular-subtyping-methylation/input/mnp_v12.5_v12.8_NIHv2_v3.1_annotation_with_OPC_subtypes.xlsx
@@ -7265,7 +7265,9 @@
       <c r="E99" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="F99" s="1"/>
+      <c r="F99" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="G99" s="1"/>
       <c r="H99" s="1" t="s">
         <v>614</v>

--- a/analyses/molecular-subtyping-methylation/input/mnp_v12.5_v12.8_NIHv2_v3.1_annotation_with_OPC_subtypes.xlsx
+++ b/analyses/molecular-subtyping-methylation/input/mnp_v12.5_v12.8_NIHv2_v3.1_annotation_with_OPC_subtypes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="1084">
   <si>
     <t xml:space="preserve">Abbreviation_internal_NIHv3</t>
   </si>
@@ -3261,6 +3261,9 @@
   </si>
   <si>
     <t xml:space="preserve">The "mc sinonasal undifferentiated carcinoma, IDH-mutant" emerges as one distinct group among the sinonasal undifferentiated carcinomas. This group includes tumors diagnosed as sinonasal undifferentiated carcinoma, olfactory neuroblastomas, neuroendocrine carcinomas or adenocarcinomas. The tumors carry an IDH2R172 mutation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
   </si>
 </sst>
 </file>
@@ -4669,7 +4672,7 @@
         <v>200</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
@@ -4704,7 +4707,7 @@
         <v>207</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
@@ -4741,7 +4744,7 @@
         <v>213</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
@@ -4778,7 +4781,7 @@
         <v>219</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
@@ -4815,7 +4818,7 @@
         <v>225</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
@@ -4850,7 +4853,7 @@
         <v>231</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
@@ -4885,7 +4888,7 @@
         <v>237</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
@@ -4920,7 +4923,7 @@
         <v>243</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1" t="s">
@@ -4955,7 +4958,7 @@
         <v>251</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
@@ -4992,7 +4995,7 @@
         <v>257</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
@@ -7266,7 +7269,7 @@
         <v>613</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>201</v>
+        <v>1083</v>
       </c>
       <c r="G99" s="1"/>
       <c r="H99" s="1" t="s">

--- a/analyses/molecular-subtyping-methylation/input/mnp_v12.5_v12.8_NIHv2_v3.1_annotation_with_OPC_subtypes.xlsx
+++ b/analyses/molecular-subtyping-methylation/input/mnp_v12.5_v12.8_NIHv2_v3.1_annotation_with_OPC_subtypes.xlsx
@@ -6962,7 +6962,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>564</v>
